--- a/Thesis_TSSP_NEWNEW_M1_Results_25_Scenarios.xlsx
+++ b/Thesis_TSSP_NEWNEW_M1_Results_25_Scenarios.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4/5/2026 10:53</t>
+          <t>4/5/2026 10:49</t>
         </is>
       </c>
     </row>
@@ -537,22 +537,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4/5/2026 15:35</t>
+          <t>4/5/2026 08:53</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4/5/2026 08:27</t>
+          <t>4/5/2026 13:01</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -574,22 +574,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4/5/2026 08:53</t>
+          <t>4/5/2026 11:01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4/5/2026 11:16</t>
+          <t>4/5/2026 09:15</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -648,12 +648,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4/5/2026 09:15</t>
+          <t>4/5/2026 15:35</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4/5/2026 15:32</t>
+          <t>4/5/2026 15:34</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -769,12 +769,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4/5/2026 11:25</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4/5/2026 10:25</t>
+          <t>4/5/2026 13:28</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -917,12 +917,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4/5/2026 10:51</t>
+          <t>4/5/2026 10:44</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4/5/2026 08:49</t>
+          <t>4/5/2026 08:50</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1018,17 +1018,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4/5/2026 15:33</t>
+          <t>4/5/2026 14:16</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4/5/2026 10:58</t>
+          <t>4/5/2026 10:19</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:15</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4/5/2026 12:52</t>
+          <t>4/5/2026 10:33</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4/5/2026 08:20</t>
+          <t>4/5/2026 08:21</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4/5/2026 15:35</t>
+          <t>4/5/2026 14:39</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1203,22 +1203,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4/5/2026 14:07</t>
+          <t>4/5/2026 09:29</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4/5/2026 13:59</t>
+          <t>4/5/2026 14:50</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>427.52 min</t>
+          <t>428.00 min</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.28 min</t>
+          <t>30.85 min</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>84.88 min</t>
+          <t>84.20 min</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15.16 min</t>
+          <t>15.00 min</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.28/3.88/8.00 min</t>
+          <t>4.64/4.80/6.52 min</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>901.6910 sec</t>
+          <t>1155.6300 sec</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.3763 %</t>
+          <t>1.9860 %</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>30.29 min | 87.00 min</t>
+          <t>30.14 min | 87.00 min</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>30.14 min | 85.00 min</t>
+          <t>29.33 min | 85.00 min</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>31.86 min | 92.00 min</t>
+          <t>31.43 min | 92.00 min</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>34.29 min | 89.00 min</t>
+          <t>31.24 min | 79.00 min</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>31.00 min | 84.00 min</t>
+          <t>30.62 min | 84.00 min</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>29.90 min | 93.00 min</t>
+          <t>29.14 min | 93.00 min</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>29.38 min | 84.00 min</t>
+          <t>29.10 min | 83.00 min</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>31.67 min | 86.00 min</t>
+          <t>32.38 min | 86.00 min</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>29.29 min | 81.00 min</t>
+          <t>29.10 min | 80.00 min</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>32.67 min | 87.00 min</t>
+          <t>31.86 min | 87.00 min</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>30.71 min | 83.00 min</t>
+          <t>29.67 min | 83.00 min</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>28.52 min | 84.00 min</t>
+          <t>28.24 min | 84.00 min</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>34.19 min | 84.00 min</t>
+          <t>33.43 min | 84.00 min</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>31.05 min | 81.00 min</t>
+          <t>30.24 min | 81.00 min</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>33.29 min | 88.00 min</t>
+          <t>32.57 min | 88.00 min</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>29.81 min | 88.00 min</t>
+          <t>30.05 min | 88.00 min</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>31.14 min | 78.00 min</t>
+          <t>31.29 min | 78.00 min</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>30.95 min | 88.00 min</t>
+          <t>30.62 min | 88.00 min</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>31.76 min | 83.00 min</t>
+          <t>32.81 min | 82.00 min</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>30.05 min | 81.00 min</t>
+          <t>29.57 min | 81.00 min</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>32.29 min | 82.00 min</t>
+          <t>32.19 min | 82.00 min</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>32.24 min | 84.00 min</t>
+          <t>31.67 min | 84.00 min</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>32.71 min | 85.00 min</t>
+          <t>33.00 min | 85.00 min</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>32.52 min | 81.00 min</t>
+          <t>31.33 min | 77.00 min</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>18.79</v>
+        <v>14.08</v>
       </c>
     </row>
     <row r="56">
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>9.4</v>
+        <v>14.08</v>
       </c>
     </row>
     <row r="57">
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>9.4</v>
+        <v>11.73</v>
       </c>
     </row>
     <row r="58">
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>11.74</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="59">
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2.25</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="60">
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4.05</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="61">
@@ -1877,7 +1877,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="62">
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>16.53</v>
+        <v>24.77</v>
       </c>
     </row>
     <row r="63">
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>28.94</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="64">
@@ -1907,7 +1907,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>41.34</v>
+        <v>33.03</v>
       </c>
     </row>
   </sheetData>
@@ -2938,22 +2938,22 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:23</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:32</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3032,25 +3032,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 09:16</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4/5/2026 09:35</t>
+          <t>4/5/2026 09:34</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4/5/2026 09:35</t>
+          <t>4/5/2026 09:34</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:36</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -3058,22 +3058,22 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:36</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>4/5/2026 09:57</t>
+          <t>4/5/2026 09:56</t>
         </is>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -3272,48 +3272,48 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4/5/2026 10:39</t>
+          <t>4/5/2026 10:42</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4/5/2026 10:48</t>
+          <t>4/5/2026 10:51</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>4/5/2026 10:48</t>
+          <t>4/5/2026 10:58</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4/5/2026 10:50</t>
+          <t>4/5/2026 11:00</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>4/5/2026 10:53</t>
+          <t>4/5/2026 11:09</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>4/5/2026 11:23</t>
+          <t>4/5/2026 11:39</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M23" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
@@ -3765,35 +3765,35 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
+          <t>4/5/2026 10:57</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
           <t>4/5/2026 10:58</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>4/5/2026 10:59</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>4/5/2026 11:09</t>
+          <t>4/5/2026 10:58</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>4/5/2026 11:21</t>
+          <t>4/5/2026 11:10</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="N31" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3838,22 +3838,22 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>4/5/2026 08:40</t>
+          <t>4/5/2026 08:39</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>4/5/2026 08:44</t>
+          <t>4/5/2026 08:43</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -3898,22 +3898,22 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>4/5/2026 11:51</t>
+          <t>4/5/2026 11:50</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>4/5/2026 11:57</t>
+          <t>4/5/2026 11:56</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -3958,22 +3958,22 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>4/5/2026 08:44</t>
+          <t>4/5/2026 08:34</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>4/5/2026 09:11</t>
+          <t>4/5/2026 09:01</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="N34" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -4198,22 +4198,22 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>4/5/2026 09:24</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>4/5/2026 09:33</t>
+          <t>4/5/2026 09:29</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -4378,22 +4378,22 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>4/5/2026 11:21</t>
+          <t>4/5/2026 11:15</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>4/5/2026 11:44</t>
+          <t>4/5/2026 11:38</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="N41" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -4712,16 +4712,16 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4/5/2026 11:47</t>
+          <t>4/5/2026 11:50</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>4/5/2026 11:49</t>
+          <t>4/5/2026 11:52</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -4798,22 +4798,22 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t>4/5/2026 09:11</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t>4/5/2026 09:12</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:13</t>
-        </is>
-      </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -5038,22 +5038,22 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>4/5/2026 11:09</t>
+          <t>4/5/2026 11:03</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>4/5/2026 11:21</t>
+          <t>4/5/2026 11:15</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="N52" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -5398,22 +5398,22 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>4/5/2026 07:51</t>
+          <t>4/5/2026 07:49</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>4/5/2026 07:55</t>
+          <t>4/5/2026 07:53</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -5518,22 +5518,22 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>4/5/2026 09:11</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -5732,25 +5732,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>4/5/2026 08:57</t>
+          <t>4/5/2026 08:56</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>4/5/2026 09:05</t>
+          <t>4/5/2026 09:04</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>4/5/2026 09:05</t>
+          <t>4/5/2026 09:04</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>4/5/2026 09:07</t>
+          <t>4/5/2026 09:06</t>
         </is>
       </c>
       <c r="I64" t="n">
@@ -5758,22 +5758,22 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>4/5/2026 09:07</t>
+          <t>4/5/2026 09:06</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>4/5/2026 09:10</t>
+          <t>4/5/2026 09:09</t>
         </is>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -5792,48 +5792,48 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>4/5/2026 08:53</t>
+          <t>4/5/2026 08:45</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>4/5/2026 09:02</t>
+          <t>4/5/2026 08:54</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 08:54</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>4/5/2026 09:11</t>
+          <t>4/5/2026 08:56</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 08:56</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>4/5/2026 10:14</t>
+          <t>4/5/2026 09:49</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="N65" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -5865,35 +5865,35 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>4/5/2026 12:08</t>
+          <t>4/5/2026 12:06</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>4/5/2026 12:09</t>
+          <t>4/5/2026 12:07</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>4/5/2026 12:09</t>
+          <t>4/5/2026 12:07</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>4/5/2026 12:55</t>
+          <t>4/5/2026 12:53</t>
         </is>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="N66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -5925,35 +5925,35 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>4/5/2026 06:09</t>
+          <t>4/5/2026 06:02</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>4/5/2026 06:11</t>
+          <t>4/5/2026 06:04</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>4/5/2026 06:14</t>
+          <t>4/5/2026 06:04</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>4/5/2026 06:16</t>
+          <t>4/5/2026 06:06</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="N67" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -6058,22 +6058,22 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t>4/5/2026 09:11</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t>4/5/2026 09:12</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:13</t>
-        </is>
-      </c>
       <c r="L69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -6298,22 +6298,22 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>4/5/2026 11:08</t>
+          <t>4/5/2026 10:59</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>4/5/2026 11:20</t>
+          <t>4/5/2026 11:11</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="N73" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -6332,48 +6332,48 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>4/5/2026 07:31</t>
+          <t>4/5/2026 07:25</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>4/5/2026 07:36</t>
+          <t>4/5/2026 07:30</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>4/5/2026 07:40</t>
+          <t>4/5/2026 07:30</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>4/5/2026 07:42</t>
+          <t>4/5/2026 07:32</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t>4/5/2026 07:32</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t>4/5/2026 07:47</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>4/5/2026 08:02</t>
-        </is>
-      </c>
       <c r="L74" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="N74" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -6465,35 +6465,35 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>4/5/2026 11:24</t>
+          <t>4/5/2026 11:23</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>4/5/2026 11:26</t>
+          <t>4/5/2026 11:25</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>4/5/2026 11:26</t>
+          <t>4/5/2026 11:25</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>4/5/2026 11:46</t>
+          <t>4/5/2026 11:45</t>
         </is>
       </c>
       <c r="L76" t="n">
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -6778,22 +6778,22 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>4/5/2026 09:14</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -7258,22 +7258,22 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>4/5/2026 10:01</t>
+          <t>4/5/2026 09:57</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>4/5/2026 10:08</t>
+          <t>4/5/2026 10:04</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="N89" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -7498,22 +7498,22 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>4/5/2026 09:31</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>4/5/2026 10:12</t>
+          <t>4/5/2026 10:11</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -7978,22 +7978,22 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>4/5/2026 09:24</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>4/5/2026 09:33</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N101" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -8265,16 +8265,16 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>4/5/2026 09:04</t>
+          <t>4/5/2026 09:05</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>4/5/2026 09:06</t>
+          <t>4/5/2026 09:07</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -8287,7 +8287,7 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
         <v>14</v>
@@ -8445,35 +8445,35 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>4/5/2026 06:09</t>
+          <t>4/5/2026 06:02</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>4/5/2026 06:11</t>
+          <t>4/5/2026 06:04</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>4/5/2026 06:14</t>
+          <t>4/5/2026 06:04</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>4/5/2026 06:16</t>
+          <t>4/5/2026 06:06</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="N109" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -8732,48 +8732,48 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>4/5/2026 12:12</t>
+          <t>4/5/2026 12:15</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>4/5/2026 12:14</t>
+          <t>4/5/2026 12:17</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>4/5/2026 12:14</t>
+          <t>4/5/2026 12:22</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>4/5/2026 12:16</t>
+          <t>4/5/2026 12:24</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>4/5/2026 12:16</t>
+          <t>4/5/2026 12:24</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>4/5/2026 12:40</t>
+          <t>4/5/2026 12:48</t>
         </is>
       </c>
       <c r="L114" t="n">
         <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="115">
@@ -8818,22 +8818,22 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>4/5/2026 10:58</t>
+          <t>4/5/2026 10:57</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>4/5/2026 11:10</t>
+          <t>4/5/2026 11:09</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -8972,48 +8972,48 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>4/5/2026 11:15</t>
+          <t>4/5/2026 11:13</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
+          <t>4/5/2026 11:21</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>4/5/2026 11:21</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
           <t>4/5/2026 11:23</t>
         </is>
       </c>
-      <c r="F118" t="n">
-        <v>2</v>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>4/5/2026 11:25</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>4/5/2026 11:27</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>4/5/2026 11:27</t>
+          <t>4/5/2026 11:23</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>4/5/2026 11:47</t>
+          <t>4/5/2026 11:43</t>
         </is>
       </c>
       <c r="L118" t="n">
         <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="N118" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -9238,22 +9238,22 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>4/5/2026 09:25</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:29</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="N122" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -9298,22 +9298,22 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>4/5/2026 09:25</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="N123" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -9658,22 +9658,22 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>4/5/2026 12:12</t>
+          <t>4/5/2026 12:11</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>4/5/2026 12:58</t>
+          <t>4/5/2026 12:57</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -10005,35 +10005,35 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>4/5/2026 10:35</t>
+          <t>4/5/2026 10:37</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>4/5/2026 10:37</t>
+          <t>4/5/2026 10:39</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>4/5/2026 10:37</t>
+          <t>4/5/2026 10:40</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>4/5/2026 11:06</t>
+          <t>4/5/2026 11:09</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136">
@@ -10078,22 +10078,22 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>4/5/2026 11:06</t>
+          <t>4/5/2026 10:58</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>4/5/2026 11:18</t>
+          <t>4/5/2026 11:10</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="N136" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -10292,48 +10292,48 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>4/5/2026 08:40</t>
+          <t>4/5/2026 08:43</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>4/5/2026 08:45</t>
+          <t>4/5/2026 08:48</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>4/5/2026 08:45</t>
+          <t>4/5/2026 08:50</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>4/5/2026 08:46</t>
+          <t>4/5/2026 08:51</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>4/5/2026 08:46</t>
+          <t>4/5/2026 08:53</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>4/5/2026 09:14</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M140" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="141">
@@ -10438,22 +10438,22 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>4/5/2026 08:40</t>
+          <t>4/5/2026 08:45</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>4/5/2026 08:48</t>
+          <t>4/5/2026 08:53</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M142" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143">
@@ -10498,22 +10498,22 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>4/5/2026 09:31</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -10558,22 +10558,22 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>4/5/2026 09:14</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M144" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -10738,22 +10738,22 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>4/5/2026 10:26</t>
+          <t>4/5/2026 10:16</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>4/5/2026 10:50</t>
+          <t>4/5/2026 10:40</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="N147" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -11012,29 +11012,29 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>4/5/2026 12:57</t>
+          <t>4/5/2026 12:52</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>4/5/2026 13:00</t>
+          <t>4/5/2026 12:55</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>4/5/2026 13:02</t>
+          <t>4/5/2026 12:59</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>4/5/2026 13:04</t>
+          <t>4/5/2026 13:01</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
@@ -11047,7 +11047,7 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M152" t="n">
         <v>44</v>
@@ -11252,48 +11252,48 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>4/5/2026 12:12</t>
+          <t>4/5/2026 12:22</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>4/5/2026 12:13</t>
+          <t>4/5/2026 12:23</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>4/5/2026 12:13</t>
+          <t>4/5/2026 12:30</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>4/5/2026 12:15</t>
+          <t>4/5/2026 12:32</t>
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>4/5/2026 12:15</t>
+          <t>4/5/2026 12:42</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>4/5/2026 12:39</t>
+          <t>4/5/2026 13:06</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M156" t="n">
+        <v>54</v>
+      </c>
+      <c r="N156" t="n">
         <v>27</v>
-      </c>
-      <c r="N156" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -11745,35 +11745,35 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:18</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>4/5/2026 09:23</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>4/5/2026 09:32</t>
+          <t>4/5/2026 09:29</t>
         </is>
       </c>
       <c r="L164" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M164" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="N164" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -11805,35 +11805,35 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>4/5/2026 09:10</t>
+          <t>4/5/2026 09:11</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>4/5/2026 09:15</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>4/5/2026 09:23</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M165" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N165" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166">
@@ -11925,35 +11925,35 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>4/5/2026 10:21</t>
+          <t>4/5/2026 10:14</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>4/5/2026 10:23</t>
+          <t>4/5/2026 10:16</t>
         </is>
       </c>
       <c r="I167" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>4/5/2026 10:23</t>
+          <t>4/5/2026 10:16</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>4/5/2026 10:50</t>
+          <t>4/5/2026 10:43</t>
         </is>
       </c>
       <c r="L167" t="n">
         <v>0</v>
       </c>
       <c r="M167" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="N167" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -12165,35 +12165,35 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>4/5/2026 12:07</t>
+          <t>4/5/2026 12:06</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>4/5/2026 12:09</t>
+          <t>4/5/2026 12:08</t>
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>4/5/2026 12:09</t>
+          <t>4/5/2026 12:08</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>4/5/2026 12:55</t>
+          <t>4/5/2026 12:54</t>
         </is>
       </c>
       <c r="L171" t="n">
         <v>0</v>
       </c>
       <c r="M171" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
@@ -13005,35 +13005,35 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
+          <t>4/5/2026 09:17</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
           <t>4/5/2026 09:18</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:19</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:18</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>4/5/2026 09:29</t>
+          <t>4/5/2026 09:27</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N185" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
@@ -13138,22 +13138,22 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:36</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>4/5/2026 09:57</t>
+          <t>4/5/2026 09:56</t>
         </is>
       </c>
       <c r="L187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M187" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188">
@@ -13232,29 +13232,29 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>4/5/2026 11:31</t>
+          <t>4/5/2026 11:28</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
+          <t>4/5/2026 11:38</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>0</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>4/5/2026 11:39</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
           <t>4/5/2026 11:41</t>
         </is>
       </c>
-      <c r="F189" t="n">
-        <v>3</v>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>4/5/2026 11:44</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>4/5/2026 11:46</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M189" t="n">
         <v>44</v>
@@ -13352,16 +13352,16 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>4/5/2026 11:43</t>
+          <t>4/5/2026 11:44</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>4/5/2026 11:51</t>
+          <t>4/5/2026 11:52</t>
         </is>
       </c>
       <c r="F191" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
@@ -13485,16 +13485,16 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>4/5/2026 12:57</t>
+          <t>4/5/2026 12:59</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>4/5/2026 12:59</t>
+          <t>4/5/2026 13:01</t>
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M193" t="n">
         <v>20</v>
@@ -13772,48 +13772,48 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>4/5/2026 09:30</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>4/5/2026 09:43</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>4/5/2026 09:48</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>4/5/2026 09:49</t>
+          <t>4/5/2026 09:34</t>
         </is>
       </c>
       <c r="I198" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>4/5/2026 09:59</t>
+          <t>4/5/2026 09:34</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>4/5/2026 10:40</t>
+          <t>4/5/2026 10:15</t>
         </is>
       </c>
       <c r="L198" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M198" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="N198" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
@@ -14218,22 +14218,22 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>4/5/2026 07:51</t>
+          <t>4/5/2026 07:50</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>4/5/2026 07:55</t>
+          <t>4/5/2026 07:54</t>
         </is>
       </c>
       <c r="L205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M205" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206">
@@ -14278,22 +14278,22 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>4/5/2026 09:23</t>
+          <t>4/5/2026 09:18</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>4/5/2026 09:32</t>
+          <t>4/5/2026 09:27</t>
         </is>
       </c>
       <c r="L206" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M206" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N206" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207">
@@ -14325,35 +14325,35 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>4/5/2026 09:10</t>
+          <t>4/5/2026 09:11</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="I207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>4/5/2026 09:15</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>4/5/2026 09:23</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="L207" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M207" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N207" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208">
@@ -14372,25 +14372,25 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>4/5/2026 09:16</t>
+          <t>4/5/2026 09:26</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>4/5/2026 09:35</t>
+          <t>4/5/2026 09:45</t>
         </is>
       </c>
       <c r="F208" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>4/5/2026 09:35</t>
+          <t>4/5/2026 09:45</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:47</t>
         </is>
       </c>
       <c r="I208" t="n">
@@ -14398,22 +14398,22 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>4/5/2026 09:39</t>
+          <t>4/5/2026 09:47</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>4/5/2026 09:59</t>
+          <t>4/5/2026 10:07</t>
         </is>
       </c>
       <c r="L208" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M208" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="N208" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="209">
@@ -14432,48 +14432,48 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>4/5/2026 08:45</t>
+          <t>4/5/2026 08:55</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>4/5/2026 08:59</t>
+          <t>4/5/2026 09:09</t>
         </is>
       </c>
       <c r="F209" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>4/5/2026 09:03</t>
+          <t>4/5/2026 09:09</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>4/5/2026 09:05</t>
+          <t>4/5/2026 09:11</t>
         </is>
       </c>
       <c r="I209" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>4/5/2026 09:39</t>
+          <t>4/5/2026 09:47</t>
         </is>
       </c>
       <c r="L209" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M209" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="N209" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="210">
@@ -14638,22 +14638,22 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>4/5/2026 08:08</t>
+          <t>4/5/2026 07:58</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>4/5/2026 08:35</t>
+          <t>4/5/2026 08:25</t>
         </is>
       </c>
       <c r="L212" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M212" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="N212" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213">
@@ -15032,48 +15032,48 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>4/5/2026 12:12</t>
+          <t>4/5/2026 12:14</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>4/5/2026 12:14</t>
+          <t>4/5/2026 12:16</t>
         </is>
       </c>
       <c r="F219" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>4/5/2026 12:14</t>
+          <t>4/5/2026 12:23</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>4/5/2026 12:16</t>
+          <t>4/5/2026 12:25</t>
         </is>
       </c>
       <c r="I219" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>4/5/2026 12:16</t>
+          <t>4/5/2026 12:25</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>4/5/2026 12:40</t>
+          <t>4/5/2026 12:49</t>
         </is>
       </c>
       <c r="L219" t="n">
         <v>0</v>
       </c>
       <c r="M219" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="N219" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="220">
@@ -15238,22 +15238,22 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>4/5/2026 08:23</t>
+          <t>4/5/2026 08:16</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>4/5/2026 08:43</t>
+          <t>4/5/2026 08:36</t>
         </is>
       </c>
       <c r="L222" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M222" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="N222" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223">
@@ -15538,22 +15538,22 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>4/5/2026 09:27</t>
+          <t>4/5/2026 09:25</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>4/5/2026 09:36</t>
+          <t>4/5/2026 09:34</t>
         </is>
       </c>
       <c r="L227" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M227" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N227" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="228">
@@ -15598,22 +15598,22 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:15</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>4/5/2026 09:27</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="L228" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M228" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="N228" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="229">
@@ -15658,22 +15658,22 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>4/5/2026 09:36</t>
+          <t>4/5/2026 09:34</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>4/5/2026 09:56</t>
+          <t>4/5/2026 09:54</t>
         </is>
       </c>
       <c r="L229" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M229" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="N229" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230">
@@ -15718,22 +15718,22 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>4/5/2026 10:21</t>
+          <t>4/5/2026 10:15</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>4/5/2026 10:48</t>
+          <t>4/5/2026 10:42</t>
         </is>
       </c>
       <c r="L230" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M230" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="N230" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="231">
@@ -16318,22 +16318,22 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>4/5/2026 09:39</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>4/5/2026 10:20</t>
+          <t>4/5/2026 10:14</t>
         </is>
       </c>
       <c r="L240" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M240" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="N240" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241">
@@ -16605,35 +16605,35 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>4/5/2026 08:46</t>
+          <t>4/5/2026 08:49</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>4/5/2026 08:48</t>
+          <t>4/5/2026 08:51</t>
         </is>
       </c>
       <c r="I245" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>4/5/2026 08:48</t>
+          <t>4/5/2026 08:52</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>4/5/2026 09:16</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="L245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M245" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="N245" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="246">
@@ -16738,22 +16738,22 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>4/5/2026 08:40</t>
+          <t>4/5/2026 08:44</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>4/5/2026 08:48</t>
+          <t>4/5/2026 08:52</t>
         </is>
       </c>
       <c r="L247" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M247" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="N247" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="248">
@@ -16798,22 +16798,22 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>4/5/2026 09:24</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>4/5/2026 09:33</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="L248" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M248" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N248" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
@@ -16858,22 +16858,22 @@
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>4/5/2026 09:16</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>4/5/2026 09:24</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="L249" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M249" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="N249" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250">
@@ -17038,22 +17038,22 @@
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>4/5/2026 10:17</t>
+          <t>4/5/2026 10:16</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>4/5/2026 10:41</t>
+          <t>4/5/2026 10:40</t>
         </is>
       </c>
       <c r="L252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M252" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253">
@@ -17158,22 +17158,22 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>4/5/2026 10:50</t>
+          <t>4/5/2026 10:49</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>4/5/2026 11:20</t>
+          <t>4/5/2026 11:19</t>
         </is>
       </c>
       <c r="L254" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M254" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N254" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="255">
@@ -17312,29 +17312,29 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>4/5/2026 12:57</t>
+          <t>4/5/2026 13:00</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>4/5/2026 13:00</t>
+          <t>4/5/2026 13:03</t>
         </is>
       </c>
       <c r="F257" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>4/5/2026 13:02</t>
+          <t>4/5/2026 13:04</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>4/5/2026 13:04</t>
+          <t>4/5/2026 13:06</t>
         </is>
       </c>
       <c r="I257" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J257" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         </is>
       </c>
       <c r="L257" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M257" t="n">
         <v>43</v>
@@ -17552,48 +17552,48 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>4/5/2026 09:30</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>4/5/2026 09:43</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="F261" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>4/5/2026 09:50</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>4/5/2026 09:51</t>
+          <t>4/5/2026 09:34</t>
         </is>
       </c>
       <c r="I261" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>4/5/2026 10:01</t>
+          <t>4/5/2026 09:34</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>4/5/2026 10:42</t>
+          <t>4/5/2026 10:15</t>
         </is>
       </c>
       <c r="L261" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M261" t="n">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="N261" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="262">
@@ -17758,22 +17758,22 @@
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>4/5/2026 11:51</t>
+          <t>4/5/2026 11:50</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>4/5/2026 11:57</t>
+          <t>4/5/2026 11:56</t>
         </is>
       </c>
       <c r="L264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M264" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="265">
@@ -18045,35 +18045,35 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:16</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:18</t>
         </is>
       </c>
       <c r="I269" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:18</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>4/5/2026 09:30</t>
+          <t>4/5/2026 09:27</t>
         </is>
       </c>
       <c r="L269" t="n">
         <v>0</v>
       </c>
       <c r="M269" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="N269" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="270">
@@ -18152,48 +18152,48 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>4/5/2026 09:16</t>
+          <t>4/5/2026 09:26</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>4/5/2026 09:33</t>
+          <t>4/5/2026 09:43</t>
         </is>
       </c>
       <c r="F271" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>4/5/2026 09:33</t>
+          <t>4/5/2026 09:45</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>4/5/2026 09:35</t>
+          <t>4/5/2026 09:47</t>
         </is>
       </c>
       <c r="I271" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>4/5/2026 09:39</t>
+          <t>4/5/2026 09:47</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>4/5/2026 09:59</t>
+          <t>4/5/2026 10:07</t>
         </is>
       </c>
       <c r="L271" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M271" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="N271" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="272">
@@ -18212,48 +18212,48 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>4/5/2026 08:48</t>
+          <t>4/5/2026 08:51</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>4/5/2026 08:59</t>
+          <t>4/5/2026 09:02</t>
         </is>
       </c>
       <c r="F272" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>4/5/2026 09:04</t>
+          <t>4/5/2026 09:09</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>4/5/2026 09:06</t>
+          <t>4/5/2026 09:11</t>
         </is>
       </c>
       <c r="I272" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>4/5/2026 09:39</t>
+          <t>4/5/2026 09:47</t>
         </is>
       </c>
       <c r="L272" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M272" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="N272" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="273">
@@ -18345,16 +18345,16 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>4/5/2026 09:05</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>4/5/2026 09:06</t>
+          <t>4/5/2026 09:04</t>
         </is>
       </c>
       <c r="I274" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J274" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         </is>
       </c>
       <c r="L274" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M274" t="n">
         <v>15</v>
@@ -18392,48 +18392,48 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>4/5/2026 07:56</t>
+          <t>4/5/2026 07:46</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>4/5/2026 08:03</t>
+          <t>4/5/2026 07:53</t>
         </is>
       </c>
       <c r="F275" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>4/5/2026 08:09</t>
+          <t>4/5/2026 07:53</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>4/5/2026 08:11</t>
+          <t>4/5/2026 07:55</t>
         </is>
       </c>
       <c r="I275" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>4/5/2026 08:16</t>
+          <t>4/5/2026 07:55</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>4/5/2026 08:43</t>
+          <t>4/5/2026 08:22</t>
         </is>
       </c>
       <c r="L275" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M275" t="n">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="N275" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="276">
@@ -18585,29 +18585,29 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
+          <t>4/5/2026 11:50</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
           <t>4/5/2026 11:52</t>
         </is>
       </c>
-      <c r="H278" t="inlineStr">
+      <c r="I278" t="n">
+        <v>1</v>
+      </c>
+      <c r="J278" t="inlineStr">
         <is>
           <t>4/5/2026 11:54</t>
         </is>
       </c>
-      <c r="I278" t="n">
-        <v>3</v>
-      </c>
-      <c r="J278" t="inlineStr">
-        <is>
-          <t>4/5/2026 11:54</t>
-        </is>
-      </c>
       <c r="K278" t="inlineStr">
         <is>
           <t>4/5/2026 11:59</t>
         </is>
       </c>
       <c r="L278" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M278" t="n">
         <v>12</v>
@@ -18825,35 +18825,35 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>4/5/2026 12:14</t>
+          <t>4/5/2026 12:18</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>4/5/2026 12:16</t>
+          <t>4/5/2026 12:20</t>
         </is>
       </c>
       <c r="I282" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>4/5/2026 12:16</t>
+          <t>4/5/2026 12:20</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>4/5/2026 12:40</t>
+          <t>4/5/2026 12:44</t>
         </is>
       </c>
       <c r="L282" t="n">
         <v>0</v>
       </c>
       <c r="M282" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="N282" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="283">
@@ -19365,16 +19365,16 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>4/5/2026 09:10</t>
+          <t>4/5/2026 09:11</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="I291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J291" t="inlineStr">
         <is>
@@ -19387,7 +19387,7 @@
         </is>
       </c>
       <c r="L291" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M291" t="n">
         <v>17</v>
@@ -19652,48 +19652,48 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>4/5/2026 10:39</t>
+          <t>4/5/2026 10:48</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>4/5/2026 10:45</t>
+          <t>4/5/2026 10:54</t>
         </is>
       </c>
       <c r="F296" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>4/5/2026 10:45</t>
+          <t>4/5/2026 11:01</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>4/5/2026 10:46</t>
+          <t>4/5/2026 11:02</t>
         </is>
       </c>
       <c r="I296" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>4/5/2026 10:56</t>
+          <t>4/5/2026 11:09</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>4/5/2026 11:26</t>
+          <t>4/5/2026 11:39</t>
         </is>
       </c>
       <c r="L296" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M296" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="N296" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="297">
@@ -19845,16 +19845,16 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>4/5/2026 12:53</t>
+          <t>4/5/2026 12:59</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>4/5/2026 12:55</t>
+          <t>4/5/2026 13:01</t>
         </is>
       </c>
       <c r="I299" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J299" t="inlineStr">
         <is>
@@ -19867,7 +19867,7 @@
         </is>
       </c>
       <c r="L299" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M299" t="n">
         <v>39</v>
@@ -19905,29 +19905,29 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>4/5/2026 09:10</t>
+          <t>4/5/2026 09:09</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
+          <t>4/5/2026 09:11</t>
+        </is>
+      </c>
+      <c r="I300" t="n">
+        <v>0</v>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
           <t>4/5/2026 09:12</t>
         </is>
       </c>
-      <c r="I300" t="n">
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:13</t>
+        </is>
+      </c>
+      <c r="L300" t="n">
         <v>1</v>
-      </c>
-      <c r="J300" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:12</t>
-        </is>
-      </c>
-      <c r="K300" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:13</t>
-        </is>
-      </c>
-      <c r="L300" t="n">
-        <v>0</v>
       </c>
       <c r="M300" t="n">
         <v>5</v>
@@ -20192,48 +20192,48 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>4/5/2026 07:27</t>
+          <t>4/5/2026 07:25</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
+          <t>4/5/2026 07:30</t>
+        </is>
+      </c>
+      <c r="F305" t="n">
+        <v>0</v>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>4/5/2026 07:30</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
           <t>4/5/2026 07:32</t>
         </is>
       </c>
-      <c r="F305" t="n">
-        <v>2</v>
-      </c>
-      <c r="G305" t="inlineStr">
-        <is>
-          <t>4/5/2026 07:37</t>
-        </is>
-      </c>
-      <c r="H305" t="inlineStr">
-        <is>
-          <t>4/5/2026 07:39</t>
-        </is>
-      </c>
       <c r="I305" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>4/5/2026 07:49</t>
+          <t>4/5/2026 07:32</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>4/5/2026 08:04</t>
+          <t>4/5/2026 07:47</t>
         </is>
       </c>
       <c r="L305" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M305" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="N305" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="306">
@@ -20565,35 +20565,35 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>4/5/2026 09:24</t>
+          <t>4/5/2026 09:17</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>4/5/2026 09:25</t>
+          <t>4/5/2026 09:18</t>
         </is>
       </c>
       <c r="I311" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>4/5/2026 09:25</t>
+          <t>4/5/2026 09:18</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:27</t>
         </is>
       </c>
       <c r="L311" t="n">
         <v>0</v>
       </c>
       <c r="M311" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="N311" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="312">
@@ -20638,22 +20638,22 @@
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>4/5/2026 09:25</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
       <c r="L312" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M312" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="N312" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="313">
@@ -20698,22 +20698,22 @@
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:36</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t>4/5/2026 09:57</t>
+          <t>4/5/2026 09:56</t>
         </is>
       </c>
       <c r="L313" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M313" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N313" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="314">
@@ -20925,35 +20925,35 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>4/5/2026 10:57</t>
+          <t>4/5/2026 10:58</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>4/5/2026 10:58</t>
+          <t>4/5/2026 10:59</t>
         </is>
       </c>
       <c r="I317" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>4/5/2026 10:58</t>
+          <t>4/5/2026 11:09</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>4/5/2026 11:32</t>
+          <t>4/5/2026 11:43</t>
         </is>
       </c>
       <c r="L317" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M317" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="N317" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="318">
@@ -21105,35 +21105,35 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>4/5/2026 08:58</t>
+          <t>4/5/2026 08:55</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>4/5/2026 09:00</t>
+          <t>4/5/2026 08:57</t>
         </is>
       </c>
       <c r="I320" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>4/5/2026 09:00</t>
+          <t>4/5/2026 08:57</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>4/5/2026 09:06</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="L320" t="n">
         <v>0</v>
       </c>
       <c r="M320" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="N320" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="321">
@@ -21838,22 +21838,22 @@
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t>4/5/2026 09:30</t>
+          <t>4/5/2026 09:28</t>
         </is>
       </c>
       <c r="L332" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M332" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N332" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="333">
@@ -22138,22 +22138,22 @@
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>4/5/2026 09:06</t>
+          <t>4/5/2026 09:05</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:08</t>
         </is>
       </c>
       <c r="L337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M337" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="338">
@@ -22352,48 +22352,48 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>4/5/2026 08:56</t>
+          <t>4/5/2026 08:53</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>4/5/2026 08:58</t>
+          <t>4/5/2026 08:55</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>4/5/2026 09:05</t>
+          <t>4/5/2026 08:55</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>4/5/2026 09:07</t>
+          <t>4/5/2026 08:57</t>
         </is>
       </c>
       <c r="I341" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 08:57</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>4/5/2026 09:23</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="L341" t="n">
+        <v>0</v>
+      </c>
+      <c r="M341" t="n">
         <v>10</v>
       </c>
-      <c r="M341" t="n">
-        <v>30</v>
-      </c>
       <c r="N341" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="342">
@@ -22618,22 +22618,22 @@
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>4/5/2026 10:41</t>
+          <t>4/5/2026 10:38</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t>4/5/2026 11:10</t>
+          <t>4/5/2026 11:07</t>
         </is>
       </c>
       <c r="L345" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M345" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="N345" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="346">
@@ -22892,48 +22892,48 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>4/5/2026 08:40</t>
+          <t>4/5/2026 08:49</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>4/5/2026 08:47</t>
+          <t>4/5/2026 08:56</t>
         </is>
       </c>
       <c r="F350" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>4/5/2026 08:47</t>
+          <t>4/5/2026 09:02</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>4/5/2026 08:49</t>
+          <t>4/5/2026 09:04</t>
         </is>
       </c>
       <c r="I350" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>4/5/2026 08:49</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 09:41</t>
         </is>
       </c>
       <c r="L350" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M350" t="n">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="N350" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="351">
@@ -23072,48 +23072,48 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
       <c r="F353" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:29</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="I353" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>4/5/2026 09:31</t>
+          <t>4/5/2026 09:41</t>
         </is>
       </c>
       <c r="K353" t="inlineStr">
         <is>
-          <t>4/5/2026 09:40</t>
+          <t>4/5/2026 09:50</t>
         </is>
       </c>
       <c r="L353" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M353" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="N353" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="354">
@@ -23158,22 +23158,22 @@
       </c>
       <c r="J354" t="inlineStr">
         <is>
+          <t>4/5/2026 09:15</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
           <t>4/5/2026 09:23</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:31</t>
-        </is>
-      </c>
       <c r="L354" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M354" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="N354" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="355">
@@ -23385,16 +23385,16 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>4/5/2026 09:03</t>
+          <t>4/5/2026 09:04</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>4/5/2026 09:05</t>
+          <t>4/5/2026 09:06</t>
         </is>
       </c>
       <c r="I358" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J358" t="inlineStr">
         <is>
@@ -23407,7 +23407,7 @@
         </is>
       </c>
       <c r="L358" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M358" t="n">
         <v>14</v>
@@ -23625,16 +23625,16 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>4/5/2026 12:53</t>
+          <t>4/5/2026 13:00</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>4/5/2026 12:54</t>
+          <t>4/5/2026 13:01</t>
         </is>
       </c>
       <c r="I362" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J362" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         </is>
       </c>
       <c r="L362" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M362" t="n">
         <v>39</v>
@@ -23685,35 +23685,35 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>4/5/2026 09:10</t>
+          <t>4/5/2026 09:09</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
+          <t>4/5/2026 09:11</t>
+        </is>
+      </c>
+      <c r="I363" t="n">
+        <v>0</v>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:11</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
           <t>4/5/2026 09:12</t>
         </is>
       </c>
-      <c r="I363" t="n">
-        <v>1</v>
-      </c>
-      <c r="J363" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:12</t>
-        </is>
-      </c>
-      <c r="K363" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:13</t>
-        </is>
-      </c>
       <c r="L363" t="n">
         <v>0</v>
       </c>
       <c r="M363" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N363" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="364">
@@ -23852,25 +23852,25 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>4/5/2026 09:32</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="F366" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>4/5/2026 09:32</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="I366" t="n">
@@ -23878,22 +23878,22 @@
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t>4/5/2026 10:15</t>
+          <t>4/5/2026 10:14</t>
         </is>
       </c>
       <c r="L366" t="n">
         <v>0</v>
       </c>
       <c r="M366" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N366" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="367">
@@ -24358,22 +24358,22 @@
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>4/5/2026 09:24</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="K374" t="inlineStr">
         <is>
-          <t>4/5/2026 09:33</t>
+          <t>4/5/2026 09:32</t>
         </is>
       </c>
       <c r="L374" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M374" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N374" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="375">
@@ -24418,22 +24418,22 @@
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>4/5/2026 09:16</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
       <c r="K375" t="inlineStr">
         <is>
-          <t>4/5/2026 09:24</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="L375" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M375" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="N375" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="376">
@@ -24778,22 +24778,22 @@
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>4/5/2026 12:11</t>
+          <t>4/5/2026 12:10</t>
         </is>
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>4/5/2026 12:57</t>
+          <t>4/5/2026 12:56</t>
         </is>
       </c>
       <c r="L381" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M381" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N381" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="382">
@@ -24945,35 +24945,35 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>4/5/2026 09:11</t>
+          <t>4/5/2026 09:16</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>4/5/2026 09:14</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="I384" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>4/5/2026 09:24</t>
+          <t>4/5/2026 09:28</t>
         </is>
       </c>
       <c r="K384" t="inlineStr">
         <is>
-          <t>4/5/2026 09:25</t>
+          <t>4/5/2026 09:29</t>
         </is>
       </c>
       <c r="L384" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M384" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="N384" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="385">
@@ -25352,48 +25352,48 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>4/5/2026 12:23</t>
+          <t>4/5/2026 12:26</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>4/5/2026 12:34</t>
+          <t>4/5/2026 12:37</t>
         </is>
       </c>
       <c r="F391" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>4/5/2026 12:34</t>
+          <t>4/5/2026 12:38</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>4/5/2026 12:36</t>
+          <t>4/5/2026 12:40</t>
         </is>
       </c>
       <c r="I391" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>4/5/2026 12:36</t>
+          <t>4/5/2026 12:40</t>
         </is>
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t>4/5/2026 13:07</t>
+          <t>4/5/2026 13:11</t>
         </is>
       </c>
       <c r="L391" t="n">
         <v>0</v>
       </c>
       <c r="M391" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="N391" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="392">
@@ -25665,35 +25665,35 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>4/5/2026 09:11</t>
+          <t>4/5/2026 09:17</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="I396" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:29</t>
         </is>
       </c>
       <c r="K396" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:37</t>
         </is>
       </c>
       <c r="L396" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M396" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="N396" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="397">
@@ -25892,25 +25892,25 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>4/5/2026 08:58</t>
+          <t>4/5/2026 08:57</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>4/5/2026 09:06</t>
+          <t>4/5/2026 09:05</t>
         </is>
       </c>
       <c r="F400" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>4/5/2026 09:15</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="I400" t="n">
@@ -25918,22 +25918,22 @@
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>4/5/2026 09:25</t>
+          <t>4/5/2026 09:24</t>
         </is>
       </c>
       <c r="K400" t="inlineStr">
         <is>
-          <t>4/5/2026 09:28</t>
+          <t>4/5/2026 09:27</t>
         </is>
       </c>
       <c r="L400" t="n">
         <v>10</v>
       </c>
       <c r="M400" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N400" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="401">
@@ -25978,22 +25978,22 @@
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>4/5/2026 08:00</t>
+          <t>4/5/2026 07:59</t>
         </is>
       </c>
       <c r="K401" t="inlineStr">
         <is>
-          <t>4/5/2026 08:27</t>
+          <t>4/5/2026 08:26</t>
         </is>
       </c>
       <c r="L401" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M401" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N401" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="402">
@@ -26878,22 +26878,22 @@
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>4/5/2026 09:26</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="K416" t="inlineStr">
         <is>
-          <t>4/5/2026 09:35</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="L416" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M416" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N416" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="417">
@@ -26938,22 +26938,22 @@
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>4/5/2026 09:18</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="K417" t="inlineStr">
         <is>
-          <t>4/5/2026 09:26</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
       <c r="L417" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M417" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="N417" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="418">
@@ -27225,35 +27225,35 @@
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>4/5/2026 10:49</t>
+          <t>4/5/2026 10:52</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>4/5/2026 10:51</t>
+          <t>4/5/2026 10:54</t>
         </is>
       </c>
       <c r="I422" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>4/5/2026 10:54</t>
+          <t>4/5/2026 11:04</t>
         </is>
       </c>
       <c r="K422" t="inlineStr">
         <is>
-          <t>4/5/2026 11:24</t>
+          <t>4/5/2026 11:34</t>
         </is>
       </c>
       <c r="L422" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M422" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="N422" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="423">
@@ -27418,22 +27418,22 @@
       </c>
       <c r="J425" t="inlineStr">
         <is>
-          <t>4/5/2026 09:58</t>
+          <t>4/5/2026 09:57</t>
         </is>
       </c>
       <c r="K425" t="inlineStr">
         <is>
-          <t>4/5/2026 10:05</t>
+          <t>4/5/2026 10:04</t>
         </is>
       </c>
       <c r="L425" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M425" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N425" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="426">
@@ -27658,22 +27658,22 @@
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>4/5/2026 10:43</t>
+          <t>4/5/2026 10:35</t>
         </is>
       </c>
       <c r="K429" t="inlineStr">
         <is>
-          <t>4/5/2026 11:12</t>
+          <t>4/5/2026 11:04</t>
         </is>
       </c>
       <c r="L429" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M429" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="N429" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="430">
@@ -28138,22 +28138,22 @@
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="K437" t="inlineStr">
         <is>
-          <t>4/5/2026 09:31</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="L437" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M437" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N437" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="438">
@@ -28425,16 +28425,16 @@
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>4/5/2026 09:03</t>
+          <t>4/5/2026 09:06</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>4/5/2026 09:05</t>
+          <t>4/5/2026 09:08</t>
         </is>
       </c>
       <c r="I442" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J442" t="inlineStr">
         <is>
@@ -28447,7 +28447,7 @@
         </is>
       </c>
       <c r="L442" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M442" t="n">
         <v>15</v>
@@ -28485,35 +28485,35 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>4/5/2026 10:56</t>
+          <t>4/5/2026 10:57</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>4/5/2026 10:57</t>
+          <t>4/5/2026 10:58</t>
         </is>
       </c>
       <c r="I443" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>4/5/2026 10:57</t>
+          <t>4/5/2026 11:08</t>
         </is>
       </c>
       <c r="K443" t="inlineStr">
         <is>
-          <t>4/5/2026 11:31</t>
+          <t>4/5/2026 11:42</t>
         </is>
       </c>
       <c r="L443" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M443" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="N443" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="444">
@@ -28652,25 +28652,25 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>4/5/2026 12:50</t>
+          <t>4/5/2026 12:51</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>4/5/2026 12:53</t>
+          <t>4/5/2026 12:54</t>
         </is>
       </c>
       <c r="F446" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>4/5/2026 12:53</t>
+          <t>4/5/2026 12:54</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>4/5/2026 12:55</t>
+          <t>4/5/2026 12:56</t>
         </is>
       </c>
       <c r="I446" t="n">
@@ -28687,7 +28687,7 @@
         </is>
       </c>
       <c r="L446" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M446" t="n">
         <v>33</v>
@@ -28918,22 +28918,22 @@
       </c>
       <c r="J450" t="inlineStr">
         <is>
-          <t>4/5/2026 10:42</t>
+          <t>4/5/2026 10:39</t>
         </is>
       </c>
       <c r="K450" t="inlineStr">
         <is>
-          <t>4/5/2026 11:11</t>
+          <t>4/5/2026 11:08</t>
         </is>
       </c>
       <c r="L450" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M450" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N450" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="451">
@@ -29038,22 +29038,22 @@
       </c>
       <c r="J452" t="inlineStr">
         <is>
-          <t>4/5/2026 07:33</t>
+          <t>4/5/2026 07:31</t>
         </is>
       </c>
       <c r="K452" t="inlineStr">
         <is>
-          <t>4/5/2026 07:48</t>
+          <t>4/5/2026 07:46</t>
         </is>
       </c>
       <c r="L452" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M452" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N452" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="453">
@@ -29145,35 +29145,35 @@
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>4/5/2026 11:40</t>
+          <t>4/5/2026 11:41</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>4/5/2026 11:41</t>
+          <t>4/5/2026 11:42</t>
         </is>
       </c>
       <c r="I454" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J454" t="inlineStr">
         <is>
-          <t>4/5/2026 11:41</t>
+          <t>4/5/2026 11:42</t>
         </is>
       </c>
       <c r="K454" t="inlineStr">
         <is>
-          <t>4/5/2026 12:05</t>
+          <t>4/5/2026 12:06</t>
         </is>
       </c>
       <c r="L454" t="n">
         <v>0</v>
       </c>
       <c r="M454" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N454" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="455">
@@ -29398,22 +29398,22 @@
       </c>
       <c r="J458" t="inlineStr">
         <is>
-          <t>4/5/2026 09:25</t>
+          <t>4/5/2026 09:17</t>
         </is>
       </c>
       <c r="K458" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:26</t>
         </is>
       </c>
       <c r="L458" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M458" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N458" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="459">
@@ -29458,22 +29458,22 @@
       </c>
       <c r="J459" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 09:15</t>
         </is>
       </c>
       <c r="K459" t="inlineStr">
         <is>
-          <t>4/5/2026 09:25</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="L459" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M459" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N459" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="460">
@@ -29612,25 +29612,25 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>4/5/2026 11:33</t>
+          <t>4/5/2026 11:34</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>4/5/2026 11:45</t>
+          <t>4/5/2026 11:46</t>
         </is>
       </c>
       <c r="F462" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>4/5/2026 11:52</t>
+          <t>4/5/2026 11:53</t>
         </is>
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>4/5/2026 11:55</t>
+          <t>4/5/2026 11:56</t>
         </is>
       </c>
       <c r="I462" t="n">
@@ -29638,22 +29638,22 @@
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>4/5/2026 12:05</t>
+          <t>4/5/2026 12:06</t>
         </is>
       </c>
       <c r="K462" t="inlineStr">
         <is>
-          <t>4/5/2026 12:30</t>
+          <t>4/5/2026 12:31</t>
         </is>
       </c>
       <c r="L462" t="n">
         <v>10</v>
       </c>
       <c r="M462" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N462" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="463">
@@ -29685,16 +29685,16 @@
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>4/5/2026 09:03</t>
+          <t>4/5/2026 09:06</t>
         </is>
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>4/5/2026 09:05</t>
+          <t>4/5/2026 09:08</t>
         </is>
       </c>
       <c r="I463" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J463" t="inlineStr">
         <is>
@@ -29707,7 +29707,7 @@
         </is>
       </c>
       <c r="L463" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M463" t="n">
         <v>15</v>
@@ -30225,16 +30225,16 @@
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>4/5/2026 13:01</t>
+          <t>4/5/2026 13:03</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>4/5/2026 13:03</t>
+          <t>4/5/2026 13:05</t>
         </is>
       </c>
       <c r="I472" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J472" t="inlineStr">
         <is>
@@ -30247,7 +30247,7 @@
         </is>
       </c>
       <c r="L472" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M472" t="n">
         <v>61</v>
@@ -30298,22 +30298,22 @@
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>4/5/2026 07:42</t>
+          <t>4/5/2026 07:32</t>
         </is>
       </c>
       <c r="K473" t="inlineStr">
         <is>
-          <t>4/5/2026 07:57</t>
+          <t>4/5/2026 07:47</t>
         </is>
       </c>
       <c r="L473" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M473" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="N473" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="474">
@@ -30405,35 +30405,35 @@
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>4/5/2026 12:37</t>
+          <t>4/5/2026 12:38</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>4/5/2026 12:39</t>
+          <t>4/5/2026 12:40</t>
         </is>
       </c>
       <c r="I475" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J475" t="inlineStr">
         <is>
-          <t>4/5/2026 12:39</t>
+          <t>4/5/2026 12:40</t>
         </is>
       </c>
       <c r="K475" t="inlineStr">
         <is>
-          <t>4/5/2026 13:10</t>
+          <t>4/5/2026 13:11</t>
         </is>
       </c>
       <c r="L475" t="n">
         <v>0</v>
       </c>
       <c r="M475" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N475" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="476">
@@ -30658,22 +30658,22 @@
       </c>
       <c r="J479" t="inlineStr">
         <is>
-          <t>4/5/2026 09:24</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="K479" t="inlineStr">
         <is>
-          <t>4/5/2026 09:33</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="L479" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M479" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N479" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="480">
@@ -31498,22 +31498,22 @@
       </c>
       <c r="J493" t="inlineStr">
         <is>
-          <t>4/5/2026 11:06</t>
+          <t>4/5/2026 10:57</t>
         </is>
       </c>
       <c r="K493" t="inlineStr">
         <is>
-          <t>4/5/2026 11:18</t>
+          <t>4/5/2026 11:09</t>
         </is>
       </c>
       <c r="L493" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M493" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="N493" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="494">
@@ -31918,22 +31918,22 @@
       </c>
       <c r="J500" t="inlineStr">
         <is>
-          <t>4/5/2026 09:24</t>
+          <t>4/5/2026 09:17</t>
         </is>
       </c>
       <c r="K500" t="inlineStr">
         <is>
-          <t>4/5/2026 09:33</t>
+          <t>4/5/2026 09:26</t>
         </is>
       </c>
       <c r="L500" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M500" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="N500" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="501">
@@ -32025,35 +32025,35 @@
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:41</t>
         </is>
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:44</t>
         </is>
       </c>
       <c r="I502" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J502" t="inlineStr">
         <is>
-          <t>4/5/2026 09:39</t>
+          <t>4/5/2026 09:50</t>
         </is>
       </c>
       <c r="K502" t="inlineStr">
         <is>
-          <t>4/5/2026 09:59</t>
+          <t>4/5/2026 10:10</t>
         </is>
       </c>
       <c r="L502" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M502" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="N502" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="503">
@@ -32072,48 +32072,48 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>4/5/2026 08:55</t>
+          <t>4/5/2026 08:53</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>4/5/2026 09:08</t>
+          <t>4/5/2026 09:06</t>
         </is>
       </c>
       <c r="F503" t="n">
+        <v>8</v>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:13</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:14</t>
+        </is>
+      </c>
+      <c r="I503" t="n">
+        <v>7</v>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:24</t>
+        </is>
+      </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:50</t>
+        </is>
+      </c>
+      <c r="L503" t="n">
         <v>10</v>
       </c>
-      <c r="G503" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:08</t>
-        </is>
-      </c>
-      <c r="H503" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:09</t>
-        </is>
-      </c>
-      <c r="I503" t="n">
-        <v>0</v>
-      </c>
-      <c r="J503" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:13</t>
-        </is>
-      </c>
-      <c r="K503" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:39</t>
-        </is>
-      </c>
-      <c r="L503" t="n">
-        <v>4</v>
-      </c>
       <c r="M503" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="N503" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="504">
@@ -32278,22 +32278,22 @@
       </c>
       <c r="J506" t="inlineStr">
         <is>
-          <t>4/5/2026 10:58</t>
+          <t>4/5/2026 10:48</t>
         </is>
       </c>
       <c r="K506" t="inlineStr">
         <is>
-          <t>4/5/2026 11:28</t>
+          <t>4/5/2026 11:18</t>
         </is>
       </c>
       <c r="L506" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M506" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="N506" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="507">
@@ -32338,22 +32338,22 @@
       </c>
       <c r="J507" t="inlineStr">
         <is>
-          <t>4/5/2026 12:06</t>
+          <t>4/5/2026 12:05</t>
         </is>
       </c>
       <c r="K507" t="inlineStr">
         <is>
-          <t>4/5/2026 12:52</t>
+          <t>4/5/2026 12:51</t>
         </is>
       </c>
       <c r="L507" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M507" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N507" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="508">
@@ -32672,48 +32672,48 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>4/5/2026 09:30</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>4/5/2026 09:42</t>
+          <t>4/5/2026 09:32</t>
         </is>
       </c>
       <c r="F513" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>4/5/2026 09:49</t>
+          <t>4/5/2026 09:32</t>
         </is>
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>4/5/2026 09:50</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="I513" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J513" t="inlineStr">
         <is>
-          <t>4/5/2026 10:00</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="K513" t="inlineStr">
         <is>
-          <t>4/5/2026 10:41</t>
+          <t>4/5/2026 10:14</t>
         </is>
       </c>
       <c r="L513" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M513" t="n">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="N513" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="514">
@@ -33178,22 +33178,22 @@
       </c>
       <c r="J521" t="inlineStr">
         <is>
-          <t>4/5/2026 09:23</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
       <c r="K521" t="inlineStr">
         <is>
-          <t>4/5/2026 09:32</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="L521" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M521" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N521" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="522">
@@ -33238,22 +33238,22 @@
       </c>
       <c r="J522" t="inlineStr">
         <is>
-          <t>4/5/2026 09:15</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="K522" t="inlineStr">
         <is>
-          <t>4/5/2026 09:23</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="L522" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M522" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N522" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="523">
@@ -33272,48 +33272,48 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>4/5/2026 09:16</t>
+          <t>4/5/2026 09:26</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>4/5/2026 09:33</t>
+          <t>4/5/2026 09:43</t>
         </is>
       </c>
       <c r="F523" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>4/5/2026 09:33</t>
+          <t>4/5/2026 09:45</t>
         </is>
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>4/5/2026 09:35</t>
+          <t>4/5/2026 09:47</t>
         </is>
       </c>
       <c r="I523" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J523" t="inlineStr">
         <is>
-          <t>4/5/2026 09:39</t>
+          <t>4/5/2026 09:47</t>
         </is>
       </c>
       <c r="K523" t="inlineStr">
         <is>
-          <t>4/5/2026 09:59</t>
+          <t>4/5/2026 10:07</t>
         </is>
       </c>
       <c r="L523" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M523" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="N523" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="524">
@@ -33332,48 +33332,48 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>4/5/2026 08:47</t>
+          <t>4/5/2026 08:50</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>4/5/2026 09:00</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="F524" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>4/5/2026 09:01</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>4/5/2026 09:03</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
       <c r="I524" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J524" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="K524" t="inlineStr">
         <is>
-          <t>4/5/2026 09:39</t>
+          <t>4/5/2026 09:47</t>
         </is>
       </c>
       <c r="L524" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M524" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="N524" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="525">
